--- a/Zzs/Assets/Excel/User.xlsx
+++ b/Zzs/Assets/Excel/User.xlsx
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>id</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -149,6 +149,22 @@
   </si>
   <si>
     <t>legend</t>
+  </si>
+  <si>
+    <t>陈家乐</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>李龙鑫</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>李</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -541,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="9" style="2"/>
@@ -704,6 +720,40 @@
         <v>20</v>
       </c>
     </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="2">
+        <v>15829354013</v>
+      </c>
+      <c r="D10" s="2">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="2">
+        <v>15596151864</v>
+      </c>
+      <c r="D11" s="2">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
